--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6805-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6805-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0FDB0AA7-226A-4A3F-AC96-35956A5EB4D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA3A5830-BE7F-4AF7-AB4F-D1ABF61C5B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{F46ECB9E-BB8D-4BDE-BF65-67E278048B3C}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{DDA624EC-0C5D-4BA9-9CC7-EF28E9108F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="6805-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1424,25 +1424,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{959576FC-EC17-4086-8A4C-73027E54FE43}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{563D6E79-4AEE-42E7-9AFD-C4BB5D8B9793}">
   <dimension ref="A1:R11"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1470,7 +1470,7 @@
       <c r="Q1" s="28"/>
       <c r="R1" s="20"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1500,7 +1500,7 @@
       <c r="Q2" s="30"/>
       <c r="R2" s="31"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1596,7 +1596,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="37">
         <v>2024</v>
       </c>
@@ -1704,7 +1704,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="35">
         <v>2023</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="37">
         <v>2022</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>2.76</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="35">
         <v>2021</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37" t="s">
         <v>29</v>
       </c>
